--- a/tia_exports/0_25_50_0/PLCTags.xlsx
+++ b/tia_exports/0_25_50_0/PLCTags.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="1" r:id="R2aadc728792245ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R57238e0cffd449f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="1" r:id="Rdd53b8e478194312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R2d3b06fa29ff467c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4151,13 +4151,13 @@
     <x:t xml:space="preserve">era INT_ALIGN_ROTFASTSPEED</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">INT_FREE_70</x:t>
+    <x:t xml:space="preserve">ASSE_INT_BWVSLOW2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">era INT_AVGDT_IND</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">INT_FREE_71</x:t>
+    <x:t xml:space="preserve">ASSE_INT_FWVSLOW2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">era INT_NHDT_IND</x:t>
